--- a/checklist_forms/035_vintage_item_condition_checklist--checklist_forms.xlsx
+++ b/checklist_forms/035_vintage_item_condition_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>item_a</t>
+          <t>item a</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>item_b</t>
+          <t>item b</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>item_c</t>
+          <t>item c</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>item_d</t>
+          <t>item d</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>item_e</t>
+          <t>item e</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>item_f</t>
+          <t>item f</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>item_g</t>
+          <t>item g</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>item_h</t>
+          <t>item h</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>item_i</t>
+          <t>item i</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>item_j</t>
+          <t>item j</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>item_k</t>
+          <t>item k</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>item_l</t>
+          <t>item l</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>item_m</t>
+          <t>item m</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>item_n</t>
+          <t>item n</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>item_o</t>
+          <t>item o</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>item_p</t>
+          <t>item p</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>item_q</t>
+          <t>item q</t>
         </is>
       </c>
     </row>
